--- a/public/sap-reporting/expansion-150-downloads/EXT-SD12-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-SD12-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R3a4f377d9ce645e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R67a6b41b78664321"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R2900a5c46a6f458b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R1da1d178dcae45a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R92793bcdbe3246b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R0c0e2aac5eca4c9a"/>
   </x:sheets>
 </x:workbook>
 </file>
